--- a/artfynd/A 19167-2026 artfynd.xlsx
+++ b/artfynd/A 19167-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>331390</v>
+        <v>144700</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511175.912690972</v>
+        <v>511176</v>
       </c>
       <c r="R2" t="n">
-        <v>7174649.940250112</v>
+        <v>7174650</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2011-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>200508</v>
+        <v>168938</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,34 +796,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dabbsjön, S om, Jmt</t>
+          <t>Dabbsjö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511175.912690972</v>
+        <v>511179</v>
       </c>
       <c r="R3" t="n">
-        <v>7174649.940250112</v>
+        <v>7174324</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-08-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +873,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>grannaturskog</t>
+          <t>Fjällgranskog</t>
         </is>
       </c>
       <c r="AN3" t="n">
@@ -907,7 +881,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>1 substratenheter # Grov granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,57 +892,56 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>525611</v>
+        <v>199916</v>
       </c>
       <c r="B4" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1506</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dabbsjön, S om, Jmt</t>
+          <t>Dabbsjö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511175.912690972</v>
+        <v>511179</v>
       </c>
       <c r="R4" t="n">
-        <v>7174649.940250112</v>
+        <v>7174324</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,22 +968,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-08-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-08-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +987,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>grannaturskog</t>
+          <t>Fjällgranskog</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1032,7 +995,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>1 substratenheter # Grov granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1043,22 +1006,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>144700</v>
+        <v>199917</v>
       </c>
       <c r="B5" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,34 +1024,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dabbsjön, S om, Jmt</t>
+          <t>Dabbsjö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511175.912690972</v>
+        <v>511293</v>
       </c>
       <c r="R5" t="n">
-        <v>7174649.940250112</v>
+        <v>7174376</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,22 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-08-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-08-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1101,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>grannaturskog</t>
+          <t>Fjällgranskog</t>
         </is>
       </c>
       <c r="AN5" t="n">
@@ -1157,7 +1109,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>1 substratenheter # Granlåga utan bark</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,22 +1120,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>421288</v>
+        <v>200508</v>
       </c>
       <c r="B6" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,38 +1138,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1588</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dabbsjö, Jmt</t>
+          <t>Dabbsjön, S om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511179.2590663353</v>
+        <v>511176</v>
       </c>
       <c r="R6" t="n">
-        <v>7174324.308749908</v>
+        <v>7174650</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,22 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,7 +1211,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Fjällgranskog</t>
+          <t>grannaturskog</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1286,7 +1219,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # Grov granlåga</t>
+          <t>1 substratenheter # granlåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1297,22 +1230,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>199917</v>
+        <v>331177</v>
       </c>
       <c r="B7" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1342,16 +1270,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dabbsjö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511292.6106814032</v>
+        <v>511460</v>
       </c>
       <c r="R7" t="n">
-        <v>7174375.654366208</v>
+        <v>7174573</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1378,22 +1311,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,19 +1327,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Fjällgranskog</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Granlåga utan bark</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1426,22 +1336,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>168938</v>
+        <v>331390</v>
       </c>
       <c r="B8" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,38 +1354,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dabbsjö, Jmt</t>
+          <t>Dabbsjön, S om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511179.2590663353</v>
+        <v>511176</v>
       </c>
       <c r="R8" t="n">
-        <v>7174324.308749908</v>
+        <v>7174650</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1507,22 +1408,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,7 +1427,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Fjällgranskog</t>
+          <t>grannaturskog</t>
         </is>
       </c>
       <c r="AN8" t="n">
@@ -1544,7 +1435,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # Grov granlåga</t>
+          <t>1 substratenheter # granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1555,22 +1446,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>364886</v>
+        <v>389697</v>
       </c>
       <c r="B9" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,21 +1464,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1606,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511292.6106814032</v>
+        <v>511179</v>
       </c>
       <c r="R9" t="n">
-        <v>7174375.654366208</v>
+        <v>7174324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,19 +1525,9 @@
           <t>2011-07-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,7 +1549,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1 substratenheter # Gammal granlåga</t>
+          <t>1 substratenheter # Grov granlåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1694,16 +1570,11 @@
         <v>364885</v>
       </c>
       <c r="B10" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1735,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511179.2590663353</v>
+        <v>511179</v>
       </c>
       <c r="R10" t="n">
-        <v>7174324.308749908</v>
+        <v>7174324</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1768,19 +1639,9 @@
           <t>2011-07-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,37 +1681,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>199916</v>
+        <v>364886</v>
       </c>
       <c r="B11" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1864,10 +1720,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511179.2590663353</v>
+        <v>511293</v>
       </c>
       <c r="R11" t="n">
-        <v>7174324.308749908</v>
+        <v>7174376</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1897,19 +1753,9 @@
           <t>2011-07-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1931,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>1 substratenheter # Grov granlåga</t>
+          <t>1 substratenheter # Gammal granlåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1949,54 +1795,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>389697</v>
+        <v>525611</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dabbsjö, Jmt</t>
+          <t>Dabbsjön, S om, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511179.2590663353</v>
+        <v>511176</v>
       </c>
       <c r="R12" t="n">
-        <v>7174324.308749908</v>
+        <v>7174650</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2023,22 +1860,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2052,7 +1879,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Fjällgranskog</t>
+          <t>grannaturskog</t>
         </is>
       </c>
       <c r="AN12" t="n">
@@ -2060,7 +1887,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # Grov granlåga</t>
+          <t>1 substratenheter # granlåga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2071,44 +1898,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1591810</v>
+        <v>421288</v>
       </c>
       <c r="B13" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1588</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2122,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511179.2590663353</v>
+        <v>511179</v>
       </c>
       <c r="R13" t="n">
-        <v>7174324.308749908</v>
+        <v>7174324</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2155,19 +1977,9 @@
           <t>2011-07-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2210,12 +2022,7 @@
         <v>1898572</v>
       </c>
       <c r="B14" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2256,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511178.8815177409</v>
+        <v>511179</v>
       </c>
       <c r="R14" t="n">
-        <v>7174658.081180385</v>
+        <v>7174658</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,19 +2096,9 @@
           <t>2011-07-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2011-07-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2328,37 +2125,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>331177</v>
+        <v>1591810</v>
       </c>
       <c r="B15" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2366,21 +2158,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dabbsjö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511459.8194083381</v>
+        <v>511179</v>
       </c>
       <c r="R15" t="n">
-        <v>7174572.697945978</v>
+        <v>7174324</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2407,22 +2194,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2011-07-30</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2011-07-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2433,6 +2210,19 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Fjällgranskog</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Grov granlåga</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2442,7 +2232,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 19167-2026 artfynd.xlsx
+++ b/artfynd/A 19167-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144700</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/168938</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/199916</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/199917</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/200508</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/331177</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/331390</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1564,6 +1604,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/389697</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1678,6 +1723,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/364885</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/364886</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1902,6 +1957,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/525611</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/421288</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2122,6 +2187,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1898572</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2236,8 +2306,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1591810</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>